--- a/inputData/inputDataHumongous.xlsx
+++ b/inputData/inputDataHumongous.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D3B002-5ADA-CB43-94DB-3E089F3DA402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A07C2CF-60AD-164D-B5E7-C5A1A4E5E13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="11960" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
   <si>
     <t>type</t>
   </si>
@@ -109,36 +109,18 @@
     <t>aalborg</t>
   </si>
   <si>
-    <t>fredericia</t>
-  </si>
-  <si>
-    <t>vejle</t>
-  </si>
-  <si>
     <t>bornholm</t>
   </si>
   <si>
     <t>køge</t>
   </si>
   <si>
-    <t>hillerød</t>
-  </si>
-  <si>
     <t>(54.931394, 9.781081)</t>
   </si>
   <si>
     <t>(57.019081, 9.957817)</t>
   </si>
   <si>
-    <t>(55.581790, 9.722994)</t>
-  </si>
-  <si>
-    <t>(55.726059, 9.574035)</t>
-  </si>
-  <si>
-    <t>(55.924974, 12.265524)</t>
-  </si>
-  <si>
     <t>(55.088776, 14.721890)</t>
   </si>
   <si>
@@ -152,6 +134,12 @@
   </si>
   <si>
     <t>stopover_allowed</t>
+  </si>
+  <si>
+    <t>viborg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">helsingør </t>
   </si>
 </sst>
 </file>
@@ -852,7 +840,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
         <v>21</v>
@@ -869,7 +857,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
         <v>22</v>
@@ -886,7 +874,7 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
         <v>23</v>
@@ -902,11 +890,8 @@
       <c r="C10">
         <v>2</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -919,25 +904,8 @@
       <c r="C11">
         <v>2</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="F11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="B14">
-        <v>11</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="F14" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -948,15 +916,15 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="D16" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="4:5">
@@ -984,7 +952,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>14</v>
@@ -999,7 +967,7 @@
         <v>17</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:6">

--- a/inputData/inputDataHumongous.xlsx
+++ b/inputData/inputDataHumongous.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A07C2CF-60AD-164D-B5E7-C5A1A4E5E13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E57E67-901C-9F46-93B6-6478D13ED225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
   <si>
     <t>type</t>
   </si>
@@ -140,6 +140,12 @@
   </si>
   <si>
     <t xml:space="preserve">helsingør </t>
+  </si>
+  <si>
+    <t>(56.408780, 9.417814)</t>
+  </si>
+  <si>
+    <t>(56.049305, 12.584406)</t>
   </si>
 </sst>
 </file>
@@ -197,7 +203,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -206,6 +212,7 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -722,7 +729,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="22.5" customWidth="1"/>
@@ -890,6 +897,9 @@
       <c r="C10">
         <v>2</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="F10" t="s">
         <v>32</v>
       </c>
@@ -904,34 +914,37 @@
       <c r="C11">
         <v>2</v>
       </c>
+      <c r="D11" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="F11" t="s">
         <v>33</v>
       </c>
     </row>
+    <row r="14" spans="1:6">
+      <c r="B14">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" t="s">
+        <v>24</v>
+      </c>
+    </row>
     <row r="15" spans="1:6">
-      <c r="B15">
-        <v>12</v>
-      </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
       <c r="D15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="D16" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="4:5">
-      <c r="E19" s="2"/>
-    </row>
-    <row r="21" spans="4:5">
-      <c r="D21" s="3"/>
+    <row r="18" spans="4:5">
+      <c r="E18" s="2"/>
+    </row>
+    <row r="20" spans="4:5">
+      <c r="D20" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/inputData/inputDataHumongous.xlsx
+++ b/inputData/inputDataHumongous.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E57E67-901C-9F46-93B6-6478D13ED225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA67466E-58F6-D94F-A088-A8A0EE0A4648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
@@ -203,7 +203,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -212,7 +212,6 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -914,7 +913,7 @@
       <c r="C11">
         <v>2</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F11" t="s">
